--- a/business_surveys/027_corporate_transformation_pulse_survey--business_surveys.xlsx
+++ b/business_surveys/027_corporate_transformation_pulse_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Company Name</t>
+          <t>What is the company name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Employee Sentiment</t>
+          <t>How would you rate the current employee sentiment?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>communication_effectiveness</t>
+          <t>manager_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Communication Effectiveness</t>
+          <t>Who is your manager?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>confidence_in_change</t>
+          <t>department_name</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Confidence in Change</t>
+          <t>What is your department name?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>department_name</t>
+          <t>departmental_effectiveness</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Department Name</t>
+          <t>How would you rate your department's overall effectiveness?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,41 +635,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>manager_name</t>
+          <t>confidence_level</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Manager Name</t>
+          <t>How confident are you in the company's transformation?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>confidence_level</t>
+          <t>change_initiative</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Confidence Level</t>
+          <t>What initiative do you think is most important for the company's transformation?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>department_name_2</t>
+          <t>team_name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Department Name</t>
+          <t>What is your team name?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>departmental_effectiveness</t>
+          <t>departmental_effectiveness_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Departmental Effectiveness</t>
+          <t>How would you rate your team's effectiveness?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,36 +732,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Confidence Level</t>
+          <t>How confident are you in your team's performance?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>manager_name_2</t>
+          <t>manager_feedback</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Manager Name</t>
+          <t>What would you like to tell your manager?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>team_name</t>
+          <t>team_performance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Team Name</t>
+          <t>How would you rate your team's performance?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>confidence_level_3</t>
+          <t>departmental_effectiveness_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Confidence Level</t>
+          <t>How effective do you think your department is in achieving its goals?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>departmental_effectiveness_2</t>
+          <t>confidence_level_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Departmental Effectiveness</t>
+          <t>How confident are you that you will achieve your goals?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>team_name_2</t>
+          <t>manager_name_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Team Name</t>
+          <t>Who is your manager's manager?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>confidence_level_4</t>
+          <t>team_name_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Confidence Level</t>
+          <t>What is your team's goal?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>departmental_effectiveness_2</t>
+          <t>confidence_level_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Departmental Effectiveness</t>
+          <t>How confident are you that you will achieve your team's goal?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>manager_name_3</t>
+          <t>departmental_effectiveness_4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Manager Name</t>
+          <t>How effective do you think your department is in achieving its goal?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>team_name_2</t>
+          <t>confidence_level_5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Team Name</t>
+          <t>How confident are you that you will achieve your department's goal?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,23 +952,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>change_initiative</t>
+          <t>manager_name_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Change Initiative</t>
+          <t>Who is your manager's manager's manager?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Team Name</t>
+          <t>Team Name 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>confidence_level_5</t>
+          <t>confidence_level_6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Confidence Level</t>
+          <t>Confidence Level 6</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>departmental_effectiveness_3</t>
+          <t>departmental_effectiveness_5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Departmental Effectiveness</t>
+          <t>Departmental Effectiveness 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,39 +1049,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>team_name_4</t>
+          <t>confidence_level_7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Team Name</t>
+          <t>Confidence Level 7</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>confidence_level_6</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Confidence Level</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
